--- a/facility_management_forms/017_restroom_supplies_reorder_form--facility_management_forms.xlsx
+++ b/facility_management_forms/017_restroom_supplies_reorder_form--facility_management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -646,8 +646,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -675,12 +675,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'same_day'}</t>
+          <t>same_day</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Same Day'}</t>
+          <t>Same Day</t>
         </is>
       </c>
     </row>
@@ -692,12 +692,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'2-5_business_days'}</t>
+          <t>2-5_business_days</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '2-5 Business Days'}</t>
+          <t>2-5 Business Days</t>
         </is>
       </c>
     </row>
@@ -709,12 +709,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'1-2_weeks'}</t>
+          <t>1-2_weeks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '1-2 weeks'}</t>
+          <t>1-2 weeks</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'paper_towels'}</t>
+          <t>paper_towels</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Paper Towels'}</t>
+          <t>Paper Towels</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'toilet_paper'}</t>
+          <t>toilet_paper</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Toilet Paper'}</t>
+          <t>Toilet Paper</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'air_freshener'}</t>
+          <t>air_freshener</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Air Freshener'}</t>
+          <t>Air Freshener</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'soap'}</t>
+          <t>soap</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Soap'}</t>
+          <t>Soap</t>
         </is>
       </c>
     </row>
